--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_biobio.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2020_biobio.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>21.46637077500854</v>
+      </c>
+      <c r="C2">
         <v>30.78340161602367</v>
-      </c>
-      <c r="C2">
-        <v>21.46637077500854</v>
       </c>
       <c r="D2">
         <v>3.248503893343192</v>
       </c>
       <c r="E2">
-        <v>20.21901322582002</v>
+        <v>14.09944359054618</v>
       </c>
       <c r="F2">
         <v>65.68154318363381</v>
       </c>
       <c r="G2">
-        <v>14.09944359054618</v>
+        <v>20.21901322582002</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.17827825720901</v>
+      </c>
+      <c r="C3">
         <v>26.2984108608714</v>
-      </c>
-      <c r="C3">
-        <v>28.17827825720901</v>
       </c>
       <c r="D3">
         <v>3.802511130008504</v>
       </c>
       <c r="E3">
-        <v>17.02419375441764</v>
+        <v>18.24112001498804</v>
       </c>
       <c r="F3">
         <v>64.73468623059433</v>
       </c>
       <c r="G3">
-        <v>18.24112001498804</v>
+        <v>17.02419375441764</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>24.95097598272915</v>
+      </c>
+      <c r="C4">
         <v>29.79580822164253</v>
-      </c>
-      <c r="C4">
-        <v>24.95097598272915</v>
       </c>
       <c r="D4">
         <v>3.356176790242724</v>
       </c>
       <c r="E4">
-        <v>19.25455729166667</v>
+        <v>16.12374441964286</v>
       </c>
       <c r="F4">
         <v>64.62169828869048</v>
       </c>
       <c r="G4">
-        <v>16.12374441964286</v>
+        <v>19.25455729166667</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>28.9866581956798</v>
+      </c>
+      <c r="C5">
         <v>42.26493011435832</v>
-      </c>
-      <c r="C5">
-        <v>28.9866581956798</v>
       </c>
       <c r="D5">
         <v>2.366027809094326</v>
       </c>
       <c r="E5">
-        <v>24.68002225932109</v>
+        <v>16.92635874605824</v>
       </c>
       <c r="F5">
         <v>58.39361899462066</v>
       </c>
       <c r="G5">
-        <v>16.92635874605824</v>
+        <v>24.68002225932109</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.63792221084954</v>
+      </c>
+      <c r="C6">
         <v>27.4628966223132</v>
-      </c>
-      <c r="C6">
-        <v>29.63792221084954</v>
       </c>
       <c r="D6">
         <v>3.641276496622408</v>
       </c>
       <c r="E6">
+        <v>18.86554279664468</v>
+      </c>
+      <c r="F6">
+        <v>63.65339197003014</v>
+      </c>
+      <c r="G6">
         <v>17.48106523332519</v>
-      </c>
-      <c r="F6">
-        <v>63.65339197003013</v>
-      </c>
-      <c r="G6">
-        <v>18.86554279664468</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>23.93946496132856</v>
+      </c>
+      <c r="C7">
         <v>33.13355877724579</v>
-      </c>
-      <c r="C7">
-        <v>23.93946496132856</v>
       </c>
       <c r="D7">
         <v>3.018088116410671</v>
       </c>
       <c r="E7">
-        <v>21.09436616716049</v>
+        <v>15.24097798051713</v>
       </c>
       <c r="F7">
         <v>63.66465585232239</v>
       </c>
       <c r="G7">
-        <v>15.24097798051713</v>
+        <v>21.09436616716049</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>26.89020381328074</v>
+      </c>
+      <c r="C8">
         <v>31.4792899408284</v>
-      </c>
-      <c r="C8">
-        <v>26.89020381328074</v>
       </c>
       <c r="D8">
         <v>3.176691729323308</v>
       </c>
       <c r="E8">
+        <v>16.97940883427433</v>
+      </c>
+      <c r="F8">
+        <v>63.14347392892727</v>
+      </c>
+      <c r="G8">
         <v>19.87711723679841</v>
-      </c>
-      <c r="F8">
-        <v>63.14347392892726</v>
-      </c>
-      <c r="G8">
-        <v>16.97940883427433</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>30.544153372985</v>
+      </c>
+      <c r="C9">
         <v>22.63855147736384</v>
-      </c>
-      <c r="C9">
-        <v>30.544153372985</v>
       </c>
       <c r="D9">
         <v>4.417243749008828</v>
       </c>
       <c r="E9">
-        <v>14.77879079069695</v>
+        <v>19.93968797118773</v>
       </c>
       <c r="F9">
         <v>65.28152123811533</v>
       </c>
       <c r="G9">
-        <v>19.93968797118773</v>
+        <v>14.77879079069695</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>28.97579948141746</v>
+      </c>
+      <c r="C10">
         <v>33.30812445980985</v>
-      </c>
-      <c r="C10">
-        <v>28.97579948141746</v>
       </c>
       <c r="D10">
         <v>3.00227051573143</v>
       </c>
       <c r="E10">
-        <v>20.5245988948805</v>
+        <v>17.85500299580587</v>
       </c>
       <c r="F10">
         <v>61.62039810931363</v>
       </c>
       <c r="G10">
-        <v>17.85500299580587</v>
+        <v>20.5245988948805</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>25.57034927583971</v>
+      </c>
+      <c r="C11">
         <v>34.29640098184021</v>
-      </c>
-      <c r="C11">
-        <v>25.57034927583971</v>
       </c>
       <c r="D11">
         <v>2.915757838641715</v>
       </c>
       <c r="E11">
+        <v>15.99478893179748</v>
+      </c>
+      <c r="F11">
+        <v>62.55209406509847</v>
+      </c>
+      <c r="G11">
         <v>21.45311700310404</v>
-      </c>
-      <c r="F11">
-        <v>62.55209406509848</v>
-      </c>
-      <c r="G11">
-        <v>15.99478893179748</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>25.43528064146621</v>
+      </c>
+      <c r="C12">
         <v>35.08018327605956</v>
-      </c>
-      <c r="C12">
-        <v>25.43528064146621</v>
       </c>
       <c r="D12">
         <v>2.850612244897959</v>
       </c>
       <c r="E12">
-        <v>21.85470634410904</v>
+        <v>15.84600014272461</v>
       </c>
       <c r="F12">
         <v>62.29929351316634</v>
       </c>
       <c r="G12">
-        <v>15.84600014272461</v>
+        <v>21.85470634410904</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>25.08285004142502</v>
+      </c>
+      <c r="C13">
         <v>31.18613642640155</v>
-      </c>
-      <c r="C13">
-        <v>25.08285004142502</v>
       </c>
       <c r="D13">
         <v>3.206553021917202</v>
       </c>
       <c r="E13">
-        <v>19.95670230626491</v>
+        <v>16.05107360607935</v>
       </c>
       <c r="F13">
         <v>63.99222408765574</v>
       </c>
       <c r="G13">
-        <v>16.05107360607935</v>
+        <v>19.95670230626491</v>
       </c>
     </row>
     <row r="14">
@@ -698,22 +698,22 @@
         </is>
       </c>
       <c r="B14">
+        <v>29.18213313536253</v>
+      </c>
+      <c r="C14">
         <v>28.82949764909676</v>
-      </c>
-      <c r="C14">
-        <v>29.18213313536253</v>
       </c>
       <c r="D14">
         <v>3.468669527896996</v>
       </c>
       <c r="E14">
-        <v>18.24517442543361</v>
+        <v>18.46834501389922</v>
       </c>
       <c r="F14">
         <v>63.28648056066716</v>
       </c>
       <c r="G14">
-        <v>18.46834501389922</v>
+        <v>18.24517442543361</v>
       </c>
     </row>
     <row r="15">
@@ -723,22 +723,22 @@
         </is>
       </c>
       <c r="B15">
+        <v>28.23392216991319</v>
+      </c>
+      <c r="C15">
         <v>27.18006305878288</v>
-      </c>
-      <c r="C15">
-        <v>28.23392216991319</v>
       </c>
       <c r="D15">
         <v>3.679167328778007</v>
       </c>
       <c r="E15">
-        <v>17.48881416224328</v>
+        <v>18.16691215296112</v>
       </c>
       <c r="F15">
         <v>64.34427368479561</v>
       </c>
       <c r="G15">
-        <v>18.16691215296112</v>
+        <v>17.48881416224328</v>
       </c>
     </row>
     <row r="16">
@@ -748,22 +748,22 @@
         </is>
       </c>
       <c r="B16">
+        <v>34.27924528301887</v>
+      </c>
+      <c r="C16">
         <v>29.79622641509434</v>
-      </c>
-      <c r="C16">
-        <v>34.27924528301887</v>
       </c>
       <c r="D16">
         <v>3.35612968591692</v>
       </c>
       <c r="E16">
-        <v>18.16007359705612</v>
+        <v>20.89236430542778</v>
       </c>
       <c r="F16">
         <v>60.9475620975161</v>
       </c>
       <c r="G16">
-        <v>20.89236430542778</v>
+        <v>18.16007359705612</v>
       </c>
     </row>
     <row r="17">
@@ -773,22 +773,22 @@
         </is>
       </c>
       <c r="B17">
+        <v>27.52897787144363</v>
+      </c>
+      <c r="C17">
         <v>34.06217070600632</v>
-      </c>
-      <c r="C17">
-        <v>27.52897787144363</v>
       </c>
       <c r="D17">
         <v>2.935808197989172</v>
       </c>
       <c r="E17">
-        <v>21.07923051842191</v>
+        <v>17.03619171829149</v>
       </c>
       <c r="F17">
         <v>61.88457776328659</v>
       </c>
       <c r="G17">
-        <v>17.03619171829149</v>
+        <v>21.07923051842191</v>
       </c>
     </row>
     <row r="18">
@@ -798,22 +798,22 @@
         </is>
       </c>
       <c r="B18">
+        <v>25.37499423085799</v>
+      </c>
+      <c r="C18">
         <v>29.61185212535192</v>
-      </c>
-      <c r="C18">
-        <v>25.37499423085799</v>
       </c>
       <c r="D18">
         <v>3.377026184538654</v>
       </c>
       <c r="E18">
+        <v>16.37235341413299</v>
+      </c>
+      <c r="F18">
+        <v>64.52160447872308</v>
+      </c>
+      <c r="G18">
         <v>19.10604210714392</v>
-      </c>
-      <c r="F18">
-        <v>64.52160447872309</v>
-      </c>
-      <c r="G18">
-        <v>16.37235341413299</v>
       </c>
     </row>
     <row r="19">
@@ -823,22 +823,22 @@
         </is>
       </c>
       <c r="B19">
+        <v>31.87282168006259</v>
+      </c>
+      <c r="C19">
         <v>25.6348246674728</v>
-      </c>
-      <c r="C19">
-        <v>31.87282168006259</v>
       </c>
       <c r="D19">
         <v>3.900943396226415</v>
       </c>
       <c r="E19">
-        <v>16.27528901734104</v>
+        <v>20.23572976878612</v>
       </c>
       <c r="F19">
         <v>63.48898121387283</v>
       </c>
       <c r="G19">
-        <v>20.23572976878612</v>
+        <v>16.27528901734104</v>
       </c>
     </row>
     <row r="20">
@@ -848,22 +848,22 @@
         </is>
       </c>
       <c r="B20">
+        <v>36.25349487418453</v>
+      </c>
+      <c r="C20">
         <v>23.95153774464119</v>
-      </c>
-      <c r="C20">
-        <v>36.25349487418453</v>
       </c>
       <c r="D20">
         <v>4.175097276264592</v>
       </c>
       <c r="E20">
-        <v>14.95055264688772</v>
+        <v>22.62943571844095</v>
       </c>
       <c r="F20">
         <v>62.42001163467132</v>
       </c>
       <c r="G20">
-        <v>22.62943571844095</v>
+        <v>14.95055264688772</v>
       </c>
     </row>
     <row r="21">
@@ -873,22 +873,22 @@
         </is>
       </c>
       <c r="B21">
+        <v>28.42748950598548</v>
+      </c>
+      <c r="C21">
         <v>25.98665946090008</v>
-      </c>
-      <c r="C21">
-        <v>28.42748950598548</v>
       </c>
       <c r="D21">
         <v>3.848128311777107</v>
       </c>
       <c r="E21">
-        <v>16.82919579246133</v>
+        <v>18.40989941412805</v>
       </c>
       <c r="F21">
         <v>64.76090479341062</v>
       </c>
       <c r="G21">
-        <v>18.40989941412805</v>
+        <v>16.82919579246133</v>
       </c>
     </row>
     <row r="22">
@@ -898,22 +898,22 @@
         </is>
       </c>
       <c r="B22">
+        <v>27.75415539234635</v>
+      </c>
+      <c r="C22">
         <v>38.57750289911094</v>
-      </c>
-      <c r="C22">
-        <v>27.75415539234635</v>
       </c>
       <c r="D22">
         <v>2.592184368737475</v>
       </c>
       <c r="E22">
-        <v>23.19312107831746</v>
+        <v>16.6860330002324</v>
       </c>
       <c r="F22">
         <v>60.12084592145015</v>
       </c>
       <c r="G22">
-        <v>16.6860330002324</v>
+        <v>23.19312107831745</v>
       </c>
     </row>
     <row r="23">
@@ -923,22 +923,22 @@
         </is>
       </c>
       <c r="B23">
+        <v>26.53521422203576</v>
+      </c>
+      <c r="C23">
         <v>27.93014840841156</v>
-      </c>
-      <c r="C23">
-        <v>26.53521422203576</v>
       </c>
       <c r="D23">
         <v>3.580360495681562</v>
       </c>
       <c r="E23">
-        <v>18.08181972500424</v>
+        <v>17.17874724155491</v>
       </c>
       <c r="F23">
         <v>64.73943303344085</v>
       </c>
       <c r="G23">
-        <v>17.17874724155491</v>
+        <v>18.08181972500424</v>
       </c>
     </row>
     <row r="24">
@@ -948,22 +948,22 @@
         </is>
       </c>
       <c r="B24">
+        <v>27.02831149433091</v>
+      </c>
+      <c r="C24">
         <v>32.64987439744721</v>
-      </c>
-      <c r="C24">
-        <v>27.02831149433091</v>
       </c>
       <c r="D24">
         <v>3.062798918694115</v>
       </c>
       <c r="E24">
-        <v>20.44729792933373</v>
+        <v>16.9267400824865</v>
       </c>
       <c r="F24">
         <v>62.62596198817977</v>
       </c>
       <c r="G24">
-        <v>16.9267400824865</v>
+        <v>20.44729792933373</v>
       </c>
     </row>
     <row r="25">
@@ -973,22 +973,22 @@
         </is>
       </c>
       <c r="B25">
+        <v>26.8804664723032</v>
+      </c>
+      <c r="C25">
         <v>31.86323880201431</v>
-      </c>
-      <c r="C25">
-        <v>26.8804664723032</v>
       </c>
       <c r="D25">
         <v>3.138412909665613</v>
       </c>
       <c r="E25">
-        <v>20.07212742511771</v>
+        <v>16.93324873943968</v>
       </c>
       <c r="F25">
         <v>62.99462383544262</v>
       </c>
       <c r="G25">
-        <v>16.93324873943968</v>
+        <v>20.07212742511771</v>
       </c>
     </row>
     <row r="26">
@@ -998,22 +998,22 @@
         </is>
       </c>
       <c r="B26">
+        <v>27.16341882366878</v>
+      </c>
+      <c r="C26">
         <v>29.73405200497542</v>
-      </c>
-      <c r="C26">
-        <v>27.16341882366878</v>
       </c>
       <c r="D26">
         <v>3.363147410358566</v>
       </c>
       <c r="E26">
-        <v>18.95126278832723</v>
+        <v>17.31284684208539</v>
       </c>
       <c r="F26">
         <v>63.73589036958737</v>
       </c>
       <c r="G26">
-        <v>17.31284684208539</v>
+        <v>18.95126278832723</v>
       </c>
     </row>
     <row r="27">
@@ -1023,22 +1023,22 @@
         </is>
       </c>
       <c r="B27">
+        <v>27.16585024492652</v>
+      </c>
+      <c r="C27">
         <v>29.82505248425472</v>
-      </c>
-      <c r="C27">
-        <v>27.16585024492652</v>
       </c>
       <c r="D27">
         <v>3.352885969028625</v>
       </c>
       <c r="E27">
-        <v>18.99794954087546</v>
+        <v>17.30409200320941</v>
       </c>
       <c r="F27">
         <v>63.69795845591513</v>
       </c>
       <c r="G27">
-        <v>17.30409200320941</v>
+        <v>18.99794954087546</v>
       </c>
     </row>
     <row r="28">
@@ -1048,22 +1048,22 @@
         </is>
       </c>
       <c r="B28">
+        <v>27.63445561871447</v>
+      </c>
+      <c r="C28">
         <v>46.91735898557062</v>
-      </c>
-      <c r="C28">
-        <v>27.63445561871447</v>
       </c>
       <c r="D28">
         <v>2.131407269338304</v>
       </c>
       <c r="E28">
-        <v>26.87875751503006</v>
+        <v>15.8316633266533</v>
       </c>
       <c r="F28">
         <v>57.28957915831663</v>
       </c>
       <c r="G28">
-        <v>15.8316633266533</v>
+        <v>26.87875751503006</v>
       </c>
     </row>
     <row r="29">
@@ -1073,22 +1073,22 @@
         </is>
       </c>
       <c r="B29">
+        <v>27.14464062778669</v>
+      </c>
+      <c r="C29">
         <v>39.86088817549492</v>
-      </c>
-      <c r="C29">
-        <v>27.14464062778669</v>
       </c>
       <c r="D29">
         <v>2.508724832214765</v>
       </c>
       <c r="E29">
-        <v>23.86800512601453</v>
+        <v>16.25373771892354</v>
       </c>
       <c r="F29">
         <v>59.87825715506194</v>
       </c>
       <c r="G29">
-        <v>16.25373771892354</v>
+        <v>23.86800512601453</v>
       </c>
     </row>
     <row r="30">
@@ -1098,22 +1098,22 @@
         </is>
       </c>
       <c r="B30">
+        <v>25.34782608695652</v>
+      </c>
+      <c r="C30">
         <v>38.1304347826087</v>
-      </c>
-      <c r="C30">
-        <v>25.34782608695652</v>
       </c>
       <c r="D30">
         <v>2.622576966932725</v>
       </c>
       <c r="E30">
-        <v>23.32446808510638</v>
+        <v>15.50531914893617</v>
       </c>
       <c r="F30">
         <v>61.17021276595744</v>
       </c>
       <c r="G30">
-        <v>15.50531914893617</v>
+        <v>23.32446808510638</v>
       </c>
     </row>
     <row r="31">
@@ -1123,22 +1123,22 @@
         </is>
       </c>
       <c r="B31">
+        <v>28.41225626740947</v>
+      </c>
+      <c r="C31">
         <v>32.80222841225627</v>
-      </c>
-      <c r="C31">
-        <v>28.41225626740947</v>
       </c>
       <c r="D31">
         <v>3.048573369565217</v>
       </c>
       <c r="E31">
-        <v>20.34694864883544</v>
+        <v>17.62388554841385</v>
       </c>
       <c r="F31">
         <v>62.0291658027507</v>
       </c>
       <c r="G31">
-        <v>17.62388554841385</v>
+        <v>20.34694864883544</v>
       </c>
     </row>
     <row r="32">
@@ -1148,22 +1148,22 @@
         </is>
       </c>
       <c r="B32">
+        <v>26.95680068434559</v>
+      </c>
+      <c r="C32">
         <v>35.57527801539778</v>
-      </c>
-      <c r="C32">
-        <v>26.95680068434559</v>
       </c>
       <c r="D32">
         <v>2.810940787496243</v>
       </c>
       <c r="E32">
-        <v>21.88815789473685</v>
+        <v>16.58552631578947</v>
       </c>
       <c r="F32">
-        <v>61.52631578947369</v>
+        <v>61.52631578947368</v>
       </c>
       <c r="G32">
-        <v>16.58552631578948</v>
+        <v>21.88815789473684</v>
       </c>
     </row>
     <row r="33">
@@ -1173,22 +1173,22 @@
         </is>
       </c>
       <c r="B33">
+        <v>26.2848415425735</v>
+      </c>
+      <c r="C33">
         <v>39.80145093547156</v>
-      </c>
-      <c r="C33">
-        <v>26.2848415425735</v>
       </c>
       <c r="D33">
         <v>2.512471220260936</v>
       </c>
       <c r="E33">
-        <v>23.96432019862982</v>
+        <v>15.8260149891949</v>
       </c>
       <c r="F33">
         <v>60.20966481217527</v>
       </c>
       <c r="G33">
-        <v>15.8260149891949</v>
+        <v>23.96432019862982</v>
       </c>
     </row>
     <row r="34">
@@ -1198,22 +1198,22 @@
         </is>
       </c>
       <c r="B34">
+        <v>40.48780487804878</v>
+      </c>
+      <c r="C34">
         <v>20.41463414634146</v>
-      </c>
-      <c r="C34">
-        <v>40.48780487804878</v>
       </c>
       <c r="D34">
         <v>4.898446833930705</v>
       </c>
       <c r="E34">
-        <v>12.68758526603001</v>
+        <v>25.16295285735941</v>
       </c>
       <c r="F34">
         <v>62.14946187661058</v>
       </c>
       <c r="G34">
-        <v>25.16295285735941</v>
+        <v>12.68758526603001</v>
       </c>
     </row>
   </sheetData>
